--- a/Avantis EU/Avantis EU.xlsx
+++ b/Avantis EU/Avantis EU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/Avantis EU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1103" documentId="8_{F0B8999D-9BF9-463A-A515-6683C4D9B0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8256345-EB5D-438F-8C6A-279260833983}"/>
+  <xr:revisionPtr revIDLastSave="1115" documentId="8_{F0B8999D-9BF9-463A-A515-6683C4D9B0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB221D0D-8E2D-4CCF-8E2C-4859B3483156}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{CB9E69B2-3CC2-4CB8-BB0A-750BABFBC08D}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="3" xr2:uid="{CB9E69B2-3CC2-4CB8-BB0A-750BABFBC08D}"/>
   </bookViews>
   <sheets>
     <sheet name="AVWC" sheetId="1" r:id="rId1"/>
@@ -124,8 +124,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -187,8 +187,8 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F514C13-E43E-4A38-B77C-C094CA1977F0}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
@@ -1280,14 +1280,24 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" t="str">
+        <f>A15</f>
+        <v>Capital gains tax</v>
+      </c>
+      <c r="B32" s="4">
+        <f>B16</f>
+        <v>3.0343616901753706E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="2">
-        <f>SUM(B28:B31)</f>
-        <v>1.1278882000265559E-2</v>
-      </c>
-      <c r="C32" s="2"/>
+      <c r="B33" s="2">
+        <f>SUM(B28:B32)</f>
+        <v>1.431324369044093E-2</v>
+      </c>
+      <c r="C33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1297,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77A5791-F48B-40BC-A7AD-7B13AED43001}">
-  <dimension ref="B2:E7"/>
+  <dimension ref="B2:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
@@ -1355,56 +1365,72 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="str">
+        <f>AVEM!A32</f>
+        <v>Capital gains tax</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <f>AVEM!B32</f>
+        <v>3.0343616901753706E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="str">
         <f>AVWC!A27</f>
         <v>Transaction costs</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C6" s="2">
         <f>AVWC!B27</f>
         <v>4.0244941557303197E-4</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D6" s="2">
         <f>AVWS!B27</f>
         <v>9.0247476164571807E-4</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E6" s="2">
         <f>AVEM!B30</f>
         <v>3.9288891499075652E-3</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="str">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="str">
         <f>AVWC!A28</f>
         <v>Lending income</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C7" s="2">
         <f>AVWC!B28</f>
         <v>0</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D7" s="2">
         <f>AVWS!B28</f>
         <v>0</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E7" s="2">
         <f>AVEM!B31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="str">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="str">
         <f>AVWC!A29</f>
         <v>Total</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C8" s="2">
         <f>AVWC!B29</f>
         <v>5.0385106183469704E-3</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D8" s="2">
         <f>AVWS!B29</f>
         <v>7.659362384401752E-3</v>
       </c>
-      <c r="E7" s="2">
-        <f>AVEM!B32</f>
-        <v>1.1278882000265559E-2</v>
+      <c r="E8" s="2">
+        <f>AVEM!B33</f>
+        <v>1.431324369044093E-2</v>
       </c>
     </row>
   </sheetData>
